--- a/data/financial_projections_18m.xlsx
+++ b/data/financial_projections_18m.xlsx
@@ -625,7 +625,7 @@
     <row r="6" ht="30" customHeight="1" s="25">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Vehicle disposal trigger</t>
+          <t>Contract length</t>
         </is>
       </c>
       <c r="B6" s="18" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>car trigger for the disposal (with no disposal revenue) of all vehicles.</t>
+          <t>Client contract length that doubles as trigger for the disposal (with no disposal revenue) of all vehicles.</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>Over-estimated fuel expense based on Swakopmund operations ratio of N$18,000 made for every N$7,000 spent on fuel</t>
+          <t>Estimated fuel expense based on Swakopmund operations ratio of N$18,000 made for every N$7,000 spent on fuel</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">For client upkeep. Part of offset (used to offset operating profit to for contracts 
+          <t xml:space="preserve">For client upkeep. Part of offset (used to offset operating profit for contracts 
 extended beyond 15months) funds accumulated paid as subsistence. </t>
         </is>
       </c>
